--- a/datasets/dict/dict_ps_ce002.xlsx
+++ b/datasets/dict/dict_ps_ce002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD6D274-C4CF-804F-81B2-9A251CFAB904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04256604-6388-B842-AB02-984D6583B9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
+  <si>
+    <t>ps_id</t>
+  </si>
+  <si>
+    <t>ruleset_id</t>
+  </si>
+  <si>
+    <t>rule_id</t>
+  </si>
+  <si>
+    <t>stage</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>component_id</t>
+  </si>
+  <si>
+    <t>pattern</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>hard_fail</t>
+  </si>
+  <si>
+    <t>rule_note</t>
+  </si>
+  <si>
+    <t>ps_ce002</t>
+  </si>
   <si>
     <t>e_id</t>
   </si>
@@ -38,63 +71,66 @@
     <t>group</t>
   </si>
   <si>
-    <t>ps_id</t>
-  </si>
-  <si>
     <t>난이도</t>
   </si>
   <si>
     <t>주제</t>
   </si>
   <si>
+    <t>disconti_allowed</t>
+  </si>
+  <si>
+    <t>e_comp_id</t>
+  </si>
+  <si>
+    <t>gloss</t>
+  </si>
+  <si>
+    <t>ce002</t>
+  </si>
+  <si>
+    <t>ㄴ/은/는데1</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>앞절의 상황·배경을 제시하고 뒤절로 이어지게 하는 연결어미</t>
+  </si>
+  <si>
+    <t>ce003</t>
+  </si>
+  <si>
+    <t>ㄴ/은/는데2</t>
+  </si>
+  <si>
+    <t>앞절과 뒤절이 대조·대립 혹은 양보적 전환, 반전되는 관계로 이어질 때 쓰는 연결어미</t>
+  </si>
+  <si>
+    <t>primary_e_id</t>
+  </si>
+  <si>
+    <t>member_e_ids</t>
+  </si>
+  <si>
+    <t>ps_canonical_form</t>
+  </si>
+  <si>
+    <t>ps_comp_id</t>
+  </si>
+  <si>
     <t>detect_ruleset_id</t>
   </si>
   <si>
     <t>verify_ruleset_id</t>
   </si>
   <si>
-    <t>gloss</t>
-  </si>
-  <si>
-    <t>ce002</t>
-  </si>
-  <si>
-    <t>ㄴ/은/는데1</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>ps_ce002</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>c1</t>
-  </si>
-  <si>
-    <t>앞절의 상황·배경을 제시하고 뒤절로 이어지게 하는 연결어미</t>
-  </si>
-  <si>
-    <t>ce003</t>
-  </si>
-  <si>
-    <t>ㄴ/은/는데2</t>
-  </si>
-  <si>
-    <t>앞절과 뒤절이 대조·대립 혹은 양보적 전환, 반전되는 관계로 이어질 때 쓰는 연결어미</t>
-  </si>
-  <si>
-    <t>primary_e_id</t>
-  </si>
-  <si>
-    <t>member_e_ids</t>
-  </si>
-  <si>
-    <t>ps_canonical_form</t>
-  </si>
-  <si>
     <t>gloss_intro</t>
   </si>
   <si>
@@ -110,15 +146,15 @@
     <t>다음 의미를 포함하는 연결어미:</t>
   </si>
   <si>
-    <t>rs_ps_ce002_d01</t>
-  </si>
-  <si>
     <t>comp_surf</t>
   </si>
   <si>
     <t>comp_id</t>
   </si>
   <si>
+    <t>bridge_id</t>
+  </si>
+  <si>
     <t>is_required</t>
   </si>
   <si>
@@ -137,81 +173,13 @@
     <t>max_gap_to_next</t>
   </si>
   <si>
+    <t>nde</t>
+  </si>
+  <si>
     <t>y</t>
   </si>
   <si>
     <t>fx</t>
-  </si>
-  <si>
-    <t>ruleset_id</t>
-  </si>
-  <si>
-    <t>rule_id</t>
-  </si>
-  <si>
-    <t>stage</t>
-  </si>
-  <si>
-    <t>target</t>
-  </si>
-  <si>
-    <t>pattern</t>
-  </si>
-  <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>hard_fail</t>
-  </si>
-  <si>
-    <t>rule_note</t>
-  </si>
-  <si>
-    <t>r_ps_ce002_d01</t>
-  </si>
-  <si>
-    <t>detect</t>
-  </si>
-  <si>
-    <t>raw_sentence</t>
-  </si>
-  <si>
-    <t>(?:는데|은데|[가-힣]데)</t>
-  </si>
-  <si>
-    <t>initial recall-first ps_ce002 surface rule; bridge/component span deferred</t>
-  </si>
-  <si>
-    <t>nde</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bridge_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ps_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ps_ce002</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>disconti_allowed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>e_comp_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>component_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ps_comp_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -681,77 +649,77 @@
   <sheetData>
     <row r="1" spans="1:9" s="3" customFormat="1" ht="19" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="7" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="9" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>12</v>
-      </c>
       <c r="G2" s="9" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="9" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -771,70 +739,68 @@
     <col min="2" max="2" width="14.85546875" style="11" customWidth="1"/>
     <col min="3" max="3" width="13" style="11" customWidth="1"/>
     <col min="4" max="4" width="17.140625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.7109375" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" style="11"/>
+    <col min="10" max="10" width="10.7109375" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>27</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G2"/>
       <c r="I2" s="11" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -860,51 +826,51 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -913,7 +879,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -939,76 +905,58 @@
   <cols>
     <col min="1" max="1" width="16.140625" style="5" customWidth="1"/>
     <col min="2" max="2" width="15.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="5" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="5" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" style="4" customWidth="1"/>
     <col min="7" max="7" width="19.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="2" customWidth="1"/>
     <col min="9" max="9" width="15.85546875" style="5" customWidth="1"/>
-    <col min="10" max="10" width="65.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="65.28515625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>50</v>
-      </c>
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/datasets/dict/dict_ps_ce002.xlsx
+++ b/datasets/dict/dict_ps_ce002.xlsx
@@ -784,6 +784,11 @@
           <t>rs_ps_ce002_d01</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>rs_ps_ce002_v01</t>
+        </is>
+      </c>
       <c r="I2" s="11" t="inlineStr">
         <is>
           <t>다음 의미를 포함하는 연결어미:</t>
@@ -925,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col width="16.140625" customWidth="1" style="5" min="1" max="1"/>
@@ -936,8 +941,8 @@
     <col width="16.42578125" customWidth="1" style="4" min="6" max="6"/>
     <col width="19.42578125" bestFit="1" customWidth="1" style="5" min="7" max="7"/>
     <col width="9" customWidth="1" style="2" min="8" max="8"/>
-    <col width="15.85546875" customWidth="1" style="5" min="9" max="9"/>
-    <col width="65.28515625" bestFit="1" customWidth="1" style="5" min="10" max="10"/>
+    <col width="15.85546875" customWidth="1" style="5" min="9" max="10"/>
+    <col width="65.28515625" bestFit="1" customWidth="1" style="5" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="19" customHeight="1" s="5">
@@ -988,6 +993,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>to_codex_note</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>rule_note</t>
         </is>
       </c>
@@ -1029,9 +1039,116 @@
       <c r="I2" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="J2" s="0" t="inlineStr">
+      <c r="J2" s="0" t="n"/>
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>bootstrap initial detect rule: Hangul syllables with jongseong ㄴ before 데; generated class only, full regex reviewed by Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ps_ce002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rs_ps_ce002_v01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>r_ps_ce002_v01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>component_text</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>^(?:텐데|근데|원데|팬데)$</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ps_ce002 systematic FP 제거: component 자체가 텐데/근데/원데/팬데이면 hard fail</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>hard fail exact component text: 텐데/근데/원데/팬데</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ps_ce002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>rs_ps_ce002_v01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>r_ps_ce002_v02</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>left_plus_component_text</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>c1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>^(?:그런데|가운데|파운데)$</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>가운데/그런데는 왼쪽 1글자+component를 합쳐야 가는데/추운데 TP를 보호할 수 있음</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>hard fail previous char plus component text: 그런데/가운데/파운데</t>
         </is>
       </c>
     </row>

--- a/datasets/dict/dict_ps_ce002.xlsx
+++ b/datasets/dict/dict_ps_ce002.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B62E5AB-4651-4C4C-AF8B-BBBD49464FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61E5032-7A22-AA41-B545-C8EE950E4808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="70">
   <si>
     <t>ps_id</t>
   </si>
@@ -137,103 +137,121 @@
     <t>주제</t>
   </si>
   <si>
+    <t>gloss</t>
+  </si>
+  <si>
+    <t>ce002</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>앞절의 상황·배경을 제시하고 뒤절로 이어지게 하는 연결어미</t>
+  </si>
+  <si>
+    <t>ce003</t>
+  </si>
+  <si>
+    <t>앞절과 뒤절이 대조·대립 혹은 양보적 전환, 반전되는 관계로 이어질 때 쓰는 연결어미</t>
+  </si>
+  <si>
+    <t>primary_e_id</t>
+  </si>
+  <si>
+    <t>member_e_ids</t>
+  </si>
+  <si>
+    <t>ce002;ce003</t>
+  </si>
+  <si>
+    <t>ㄴ/은/는데</t>
+  </si>
+  <si>
+    <t>is_required</t>
+  </si>
+  <si>
+    <t>anchor_rank</t>
+  </si>
+  <si>
+    <t>comp_order</t>
+  </si>
+  <si>
+    <t>order_policy</t>
+  </si>
+  <si>
+    <t>min_gap_to_next</t>
+  </si>
+  <si>
+    <t>max_gap_to_next</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>fx</t>
+  </si>
+  <si>
+    <t>nde</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ps_canonical_form</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴ/은/는데1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴ/은/는데2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>disconti_allowed</t>
-  </si>
-  <si>
-    <t>gloss</t>
-  </si>
-  <si>
-    <t>ce002</t>
-  </si>
-  <si>
-    <t>ㄴ/은/는데1</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>앞절의 상황·배경을 제시하고 뒤절로 이어지게 하는 연결어미</t>
-  </si>
-  <si>
-    <t>ce003</t>
-  </si>
-  <si>
-    <t>ㄴ/은/는데2</t>
-  </si>
-  <si>
-    <t>앞절과 뒤절이 대조·대립 혹은 양보적 전환, 반전되는 관계로 이어질 때 쓰는 연결어미</t>
-  </si>
-  <si>
-    <t>primary_e_id</t>
-  </si>
-  <si>
-    <t>member_e_ids</t>
-  </si>
-  <si>
-    <t>ps_canonical_form</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ps_comp_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>detect_ruleset_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>verify_ruleset_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>gloss_intro</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>note</t>
-  </si>
-  <si>
-    <t>ce002;ce003</t>
-  </si>
-  <si>
-    <t>ㄴ/은/는데</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>다음 의미를 포함하는 연결어미:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>comp_surf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>comp_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>bridge_id</t>
-  </si>
-  <si>
-    <t>is_required</t>
-  </si>
-  <si>
-    <t>anchor_rank</t>
-  </si>
-  <si>
-    <t>comp_order</t>
-  </si>
-  <si>
-    <t>order_policy</t>
-  </si>
-  <si>
-    <t>min_gap_to_next</t>
-  </si>
-  <si>
-    <t>max_gap_to_next</t>
-  </si>
-  <si>
-    <t>nde</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>fx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -348,28 +366,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -729,41 +726,41 @@
         <v>35</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -796,31 +793,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -828,19 +825,19 @@
         <v>11</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -849,7 +846,7 @@
         <v>18</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -878,31 +875,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -910,16 +907,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -928,7 +925,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:10">

--- a/datasets/dict/dict_ps_ce002.xlsx
+++ b/datasets/dict/dict_ps_ce002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61E5032-7A22-AA41-B545-C8EE950E4808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591C0451-F67F-1543-A89C-482A1BC74F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="detect_rules" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">detect_rules!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">detect_rules!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">items!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="72">
   <si>
     <t>ps_id</t>
   </si>
@@ -41,216 +41,226 @@
     <t>stage</t>
   </si>
   <si>
+    <t>component_id</t>
+  </si>
+  <si>
+    <t>pattern</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>hard_fail</t>
+  </si>
+  <si>
+    <t>rule_note</t>
+  </si>
+  <si>
+    <t>ps_ce002</t>
+  </si>
+  <si>
+    <t>rs_ps_ce002_d01</t>
+  </si>
+  <si>
+    <t>r_ps_ce002_d01</t>
+  </si>
+  <si>
+    <t>detect</t>
+  </si>
+  <si>
+    <t>raw_sentence</t>
+  </si>
+  <si>
+    <t>[간갠갼걘건겐견곈곤관괜괸굔군권궨귄균근긘긴깐깬꺈꺤껀껜껸꼔꼰꽌꽨꾄꾠꾼꿘꿴뀐뀬끈끤낀난낸냔냰넌넨년녠논놘놴뇐뇬눈눤뉀뉜뉸는늰닌단댄댠댼던덴뎐뎬돈돤됀된됸둔둰뒌뒨듄든듼딘딴땐땬떈떤뗀뗜뗸똔똰뙌뙨뚄뚠뚼뛘뛴뜐뜬띈띤란랜랸럔런렌련롄론롼뢘뢴룐룬뤈뤤륀륜른릔린만맨먄먠먼멘면몐몬뫈뫤묀묜문뭔뭰뮌뮨믄믠민반밴뱐뱬번벤변볜본봔봰뵌뵨분붠붼뷘뷴븐븬빈빤뺀뺜뺸뻔뻰뼌뼨뽄뽠뽼뾘뾴뿐뿬쀈쀤쁀쁜쁸삔산샌샨섄선센션셴손솬쇈쇤숀순숸쉔쉰슌슨싄신싼쌘쌴썐썬쎈쎤쏀쏜쏸쐔쐰쑌쑨쒄쒠쒼쓘쓴씐씬안앤얀얜언엔연옌온완왠왼욘운원웬윈윤은읜인잔잰쟌쟨전젠젼졘존좐좬죈죤준줜줸쥔쥰즌즨진짠짼쨘쨴쩐쩬쪈쪤쫀쫜쫸쬔쬰쭌쭨쮄쮠쮼쯘쯴찐찬챈챤첀천첸쳔쳰촌촨쵄쵠쵼춘춴췐췬츈츤칀친칸캔캰컌컨켄켠켼콘콴쾐쾬쿈쿤퀀퀜퀸큔큰킌킨탄탠탼턘턴텐텬톈톤퇀퇜퇸툔툰퉌퉨튄튠튼틘틴판팬퍈퍤펀펜편폔폰퐌퐨푄푠푼풘풴퓐퓬픈픤핀한핸햔햰헌헨현혠혼환홴횐횬훈훤휀휜휸흔흰힌]데</t>
+  </si>
+  <si>
+    <t>bootstrap initial detect rule: Hangul syllables with jongseong ㄴ before 데; generated class only, full regex reviewed by Codex</t>
+  </si>
+  <si>
+    <t>rs_ps_ce002_v01</t>
+  </si>
+  <si>
+    <t>r_ps_ce002_v01</t>
+  </si>
+  <si>
+    <t>verify</t>
+  </si>
+  <si>
+    <t>component_text</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>^(?:텐데|근데|원데|팬데)$</t>
+  </si>
+  <si>
+    <t>ps_ce002 systematic FP 제거: component 자체가 텐데/근데/원데/팬데이면 hard fail</t>
+  </si>
+  <si>
+    <t>hard fail exact component text: 텐데/근데/원데/팬데</t>
+  </si>
+  <si>
+    <t>r_ps_ce002_v02</t>
+  </si>
+  <si>
+    <t>left_plus_component_text</t>
+  </si>
+  <si>
+    <t>^(?:그런데|가운데|파운데)$</t>
+  </si>
+  <si>
+    <t>가운데/그런데는 왼쪽 1글자+component를 합쳐야 가는데/추운데 TP를 보호할 수 있음</t>
+  </si>
+  <si>
+    <t>hard fail previous char plus component text: 그런데/가운데/파운데</t>
+  </si>
+  <si>
+    <t>e_id</t>
+  </si>
+  <si>
+    <t>canonical_form</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>난이도</t>
+  </si>
+  <si>
+    <t>주제</t>
+  </si>
+  <si>
+    <t>gloss</t>
+  </si>
+  <si>
+    <t>ce002</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>앞절의 상황·배경을 제시하고 뒤절로 이어지게 하는 연결어미</t>
+  </si>
+  <si>
+    <t>ce003</t>
+  </si>
+  <si>
+    <t>앞절과 뒤절이 대조·대립 혹은 양보적 전환, 반전되는 관계로 이어질 때 쓰는 연결어미</t>
+  </si>
+  <si>
+    <t>primary_e_id</t>
+  </si>
+  <si>
+    <t>member_e_ids</t>
+  </si>
+  <si>
+    <t>ce002;ce003</t>
+  </si>
+  <si>
+    <t>ㄴ/은/는데</t>
+  </si>
+  <si>
+    <t>is_required</t>
+  </si>
+  <si>
+    <t>anchor_rank</t>
+  </si>
+  <si>
+    <t>comp_order</t>
+  </si>
+  <si>
+    <t>order_policy</t>
+  </si>
+  <si>
+    <t>min_gap_to_next</t>
+  </si>
+  <si>
+    <t>max_gap_to_next</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>fx</t>
+  </si>
+  <si>
+    <t>nde</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ps_canonical_form</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴ/은/는데1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄴ/은/는데2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>disconti_allowed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ps_comp_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>detect_ruleset_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>verify_ruleset_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>gloss_intro</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>note</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 의미를 포함하는 연결어미:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>comp_surf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>comp_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bridge_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ps_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>context_chars</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>target</t>
-  </si>
-  <si>
-    <t>component_id</t>
-  </si>
-  <si>
-    <t>pattern</t>
-  </si>
-  <si>
-    <t>priority</t>
-  </si>
-  <si>
-    <t>hard_fail</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>to_codex_note</t>
-  </si>
-  <si>
-    <t>rule_note</t>
-  </si>
-  <si>
-    <t>ps_ce002</t>
-  </si>
-  <si>
-    <t>rs_ps_ce002_d01</t>
-  </si>
-  <si>
-    <t>r_ps_ce002_d01</t>
-  </si>
-  <si>
-    <t>detect</t>
-  </si>
-  <si>
-    <t>raw_sentence</t>
-  </si>
-  <si>
-    <t>[간갠갼걘건겐견곈곤관괜괸굔군권궨귄균근긘긴깐깬꺈꺤껀껜껸꼔꼰꽌꽨꾄꾠꾼꿘꿴뀐뀬끈끤낀난낸냔냰넌넨년녠논놘놴뇐뇬눈눤뉀뉜뉸는늰닌단댄댠댼던덴뎐뎬돈돤됀된됸둔둰뒌뒨듄든듼딘딴땐땬떈떤뗀뗜뗸똔똰뙌뙨뚄뚠뚼뛘뛴뜐뜬띈띤란랜랸럔런렌련롄론롼뢘뢴룐룬뤈뤤륀륜른릔린만맨먄먠먼멘면몐몬뫈뫤묀묜문뭔뭰뮌뮨믄믠민반밴뱐뱬번벤변볜본봔봰뵌뵨분붠붼뷘뷴븐븬빈빤뺀뺜뺸뻔뻰뼌뼨뽄뽠뽼뾘뾴뿐뿬쀈쀤쁀쁜쁸삔산샌샨섄선센션셴손솬쇈쇤숀순숸쉔쉰슌슨싄신싼쌘쌴썐썬쎈쎤쏀쏜쏸쐔쐰쑌쑨쒄쒠쒼쓘쓴씐씬안앤얀얜언엔연옌온완왠왼욘운원웬윈윤은읜인잔잰쟌쟨전젠젼졘존좐좬죈죤준줜줸쥔쥰즌즨진짠짼쨘쨴쩐쩬쪈쪤쫀쫜쫸쬔쬰쭌쭨쮄쮠쮼쯘쯴찐찬챈챤첀천첸쳔쳰촌촨쵄쵠쵼춘춴췐췬츈츤칀친칸캔캰컌컨켄켠켼콘콴쾐쾬쿈쿤퀀퀜퀸큔큰킌킨탄탠탼턘턴텐텬톈톤퇀퇜퇸툔툰퉌퉨튄튠튼틘틴판팬퍈퍤펀펜편폔폰퐌퐨푄푠푼풘풴퓐퓬픈픤핀한핸햔햰헌헨현혠혼환홴횐횬훈훤휀휜휸흔흰힌]데</t>
-  </si>
-  <si>
-    <t>bootstrap initial detect rule: Hangul syllables with jongseong ㄴ before 데; generated class only, full regex reviewed by Codex</t>
-  </si>
-  <si>
-    <t>rs_ps_ce002_v01</t>
-  </si>
-  <si>
-    <t>r_ps_ce002_v01</t>
-  </si>
-  <si>
-    <t>verify</t>
-  </si>
-  <si>
-    <t>component_text</t>
-  </si>
-  <si>
-    <t>c1</t>
-  </si>
-  <si>
-    <t>^(?:텐데|근데|원데|팬데)$</t>
-  </si>
-  <si>
-    <t>ps_ce002 systematic FP 제거: component 자체가 텐데/근데/원데/팬데이면 hard fail</t>
-  </si>
-  <si>
-    <t>hard fail exact component text: 텐데/근데/원데/팬데</t>
-  </si>
-  <si>
-    <t>r_ps_ce002_v02</t>
-  </si>
-  <si>
-    <t>left_plus_component_text</t>
-  </si>
-  <si>
-    <t>^(?:그런데|가운데|파운데)$</t>
-  </si>
-  <si>
-    <t>가운데/그런데는 왼쪽 1글자+component를 합쳐야 가는데/추운데 TP를 보호할 수 있음</t>
-  </si>
-  <si>
-    <t>hard fail previous char plus component text: 그런데/가운데/파운데</t>
-  </si>
-  <si>
-    <t>e_id</t>
-  </si>
-  <si>
-    <t>canonical_form</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>난이도</t>
-  </si>
-  <si>
-    <t>주제</t>
-  </si>
-  <si>
-    <t>gloss</t>
-  </si>
-  <si>
-    <t>ce002</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>앞절의 상황·배경을 제시하고 뒤절로 이어지게 하는 연결어미</t>
-  </si>
-  <si>
-    <t>ce003</t>
-  </si>
-  <si>
-    <t>앞절과 뒤절이 대조·대립 혹은 양보적 전환, 반전되는 관계로 이어질 때 쓰는 연결어미</t>
-  </si>
-  <si>
-    <t>primary_e_id</t>
-  </si>
-  <si>
-    <t>member_e_ids</t>
-  </si>
-  <si>
-    <t>ce002;ce003</t>
-  </si>
-  <si>
-    <t>ㄴ/은/는데</t>
-  </si>
-  <si>
-    <t>is_required</t>
-  </si>
-  <si>
-    <t>anchor_rank</t>
-  </si>
-  <si>
-    <t>comp_order</t>
-  </si>
-  <si>
-    <t>order_policy</t>
-  </si>
-  <si>
-    <t>min_gap_to_next</t>
-  </si>
-  <si>
-    <t>max_gap_to_next</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>fx</t>
-  </si>
-  <si>
-    <t>nde</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ps_canonical_form</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴ/은/는데1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㄴ/은/는데2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>disconti_allowed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ps_comp_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>c1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>detect_ruleset_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>verify_ruleset_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>gloss_intro</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>note</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>다음 의미를 포함하는 연결어미:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>comp_surf</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>comp_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bridge_id</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -708,59 +718,59 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="19" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -793,60 +803,60 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>39</v>
-      </c>
       <c r="F2" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -875,48 +885,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -925,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -946,7 +956,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16.140625" style="5" customWidth="1"/>
@@ -954,16 +964,16 @@
     <col min="3" max="3" width="15.42578125" style="5" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="2" customWidth="1"/>
-    <col min="9" max="10" width="15.85546875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="65.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="16.42578125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="44.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="9" style="2" customWidth="1"/>
+    <col min="10" max="11" width="15.85546875" style="5" customWidth="1"/>
+    <col min="12" max="12" width="65.28515625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19" customHeight="1">
+    <row r="1" spans="1:12" ht="19" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -975,129 +985,134 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2"/>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="H2">
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3">
         <v>10</v>
       </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2"/>
-      <c r="K2" t="s">
-        <v>17</v>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3" t="b">
+      <c r="G4"/>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4">
+        <v>20</v>
+      </c>
+      <c r="J4" t="b">
         <v>1</v>
       </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="K4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="L4" t="s">
         <v>28</v>
-      </c>
-      <c r="H4">
-        <v>20</v>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:I1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/datasets/dict/dict_ps_ce002.xlsx
+++ b/datasets/dict/dict_ps_ce002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yonghyunnam/coding/HanTalk_group/HanTalk/rule_example_auto/datasets/dict/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591C0451-F67F-1543-A89C-482A1BC74F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE2ABEE-CC3A-AB40-A6F6-6FFD9AE4DE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="21700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
